--- a/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/StructureDefinition-as-dp-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10604" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10604" uniqueCount="916">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T13:25:16+00:00</t>
+    <t>2024-04-25T11:50:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1180,7 +1180,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="IDNST"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1297,7 +1297,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>http://interopsante.org/CodeSystem/fr-v2-0203</t>
+    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1442,7 +1442,7 @@
     <t>Organization.identifier:sirene.system</t>
   </si>
   <si>
-    <t>http://sirene.fr</t>
+    <t>https://sirene.fr</t>
   </si>
   <si>
     <t>Organization.identifier:sirene.value</t>
@@ -1517,7 +1517,7 @@
     <t>Organization.identifier:finess.system</t>
   </si>
   <si>
-    <t>http://finess.esante.gouv.fr</t>
+    <t>https://finess.esante.gouv.fr</t>
   </si>
   <si>
     <t>Organization.identifier:finess.value</t>
@@ -1548,6 +1548,88 @@
   </si>
   <si>
     <t>Organization.identifier:adeliRang.type</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
+    &lt;code value="INTRN"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRang.system</t>
+  </si>
+  <si>
+    <t>https://adelirang.esante.gouv.fr</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRang.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRang.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRang.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier:rppsRang</t>
+  </si>
+  <si>
+    <t>rppsRang</t>
+  </si>
+  <si>
+    <t>RPPS rang (11 chiffres RPPS + 2 chiffres RANG)</t>
+  </si>
+  <si>
+    <t>Organization.identifier:rppsRang.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:rppsRang.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:rppsRang.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:rppsRang.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier:rppsRang.system</t>
+  </si>
+  <si>
+    <t>https://rppsrang.esante.gouv.fr</t>
+  </si>
+  <si>
+    <t>Organization.identifier:rppsRang.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:rppsRang.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier:rppsRang.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier:identifiantInterne</t>
+  </si>
+  <si>
+    <t>identifiantInterne</t>
+  </si>
+  <si>
+    <t>Identifiant interne à porté nationale des structures enregistrées au RPPS sans aucun identifiant métier.
+Il est composé de 14 chiffres.
+Il s’agit généralement de structures enregistrées temporairement par les ordres, en attente de vérification ou de changement d’identifiant.</t>
+  </si>
+  <si>
+    <t>Organization.identifier:identifiantInterne.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:identifiantInterne.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:identifiantInterne.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:identifiantInterne.type</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -1556,80 +1638,6 @@
     &lt;code value="INTRN"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Organization.identifier:adeliRang.system</t>
-  </si>
-  <si>
-    <t>https://adelirang.esante.gouv.fr</t>
-  </si>
-  <si>
-    <t>Organization.identifier:adeliRang.value</t>
-  </si>
-  <si>
-    <t>Organization.identifier:adeliRang.period</t>
-  </si>
-  <si>
-    <t>Organization.identifier:adeliRang.assigner</t>
-  </si>
-  <si>
-    <t>Organization.identifier:rppsRang</t>
-  </si>
-  <si>
-    <t>rppsRang</t>
-  </si>
-  <si>
-    <t>RPPS rang (11 chiffres RPPS + 2 chiffres RANG)</t>
-  </si>
-  <si>
-    <t>Organization.identifier:rppsRang.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:rppsRang.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:rppsRang.use</t>
-  </si>
-  <si>
-    <t>Organization.identifier:rppsRang.type</t>
-  </si>
-  <si>
-    <t>Organization.identifier:rppsRang.system</t>
-  </si>
-  <si>
-    <t>https://rppsrang.esante.gouv.fr</t>
-  </si>
-  <si>
-    <t>Organization.identifier:rppsRang.value</t>
-  </si>
-  <si>
-    <t>Organization.identifier:rppsRang.period</t>
-  </si>
-  <si>
-    <t>Organization.identifier:rppsRang.assigner</t>
-  </si>
-  <si>
-    <t>Organization.identifier:identifiantInterne</t>
-  </si>
-  <si>
-    <t>identifiantInterne</t>
-  </si>
-  <si>
-    <t>Identifiant interne à porté nationale des structures enregistrées au RPPS sans aucun identifiant métier.
-Il est composé de 14 chiffres.
-Il s’agit généralement de structures enregistrées temporairement par les ordres, en attente de vérification ou de changement d’identifiant.</t>
-  </si>
-  <si>
-    <t>Organization.identifier:identifiantInterne.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:identifiantInterne.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:identifiantInterne.use</t>
-  </si>
-  <si>
-    <t>Organization.identifier:identifiantInterne.type</t>
   </si>
   <si>
     <t>Organization.identifier:identifiantInterne.system</t>
@@ -16985,7 +16993,7 @@
         <v>78</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>495</v>
+        <v>520</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>78</v>
@@ -17056,7 +17064,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>329</v>
@@ -17104,7 +17112,7 @@
         <v>78</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>334</v>
@@ -17175,7 +17183,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>339</v>
@@ -17292,7 +17300,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>348</v>
@@ -17407,7 +17415,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>355</v>
@@ -17524,10 +17532,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17553,67 +17561,67 @@
         <v>441</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q123" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="R123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF123" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="P123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q123" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="R123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17631,24 +17639,24 @@
         <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17674,16 +17682,16 @@
         <v>320</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -17711,16 +17719,16 @@
         <v>165</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AC124" s="2"/>
       <c r="AD124" t="s" s="2">
@@ -17730,7 +17738,7 @@
         <v>116</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17748,27 +17756,27 @@
         <v>78</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>78</v>
@@ -17793,16 +17801,16 @@
         <v>320</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>78</v>
@@ -17831,7 +17839,7 @@
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>78</v>
@@ -17849,7 +17857,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17867,24 +17875,24 @@
         <v>78</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17996,10 +18004,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18111,13 +18119,13 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="B128" t="s" s="2">
-        <v>553</v>
-      </c>
       <c r="C128" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>78</v>
@@ -18139,13 +18147,13 @@
         <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -18228,10 +18236,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18343,10 +18351,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18458,10 +18466,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18501,7 +18509,7 @@
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>78</v>
@@ -18575,10 +18583,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18607,7 +18615,7 @@
         <v>230</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -18619,7 +18627,7 @@
         <v>78</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>78</v>
@@ -18638,7 +18646,7 @@
       </c>
       <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>78</v>
@@ -18688,10 +18696,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18807,10 +18815,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18922,10 +18930,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19039,10 +19047,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19158,10 +19166,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19275,10 +19283,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19304,7 +19312,7 @@
         <v>175</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M138" t="s" s="2">
         <v>426</v>
@@ -19392,10 +19400,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19509,10 +19517,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19628,10 +19636,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19747,13 +19755,13 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>78</v>
@@ -19778,16 +19786,16 @@
         <v>320</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
@@ -19816,7 +19824,7 @@
       </c>
       <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>78</v>
@@ -19834,7 +19842,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19852,24 +19860,24 @@
         <v>78</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19981,10 +19989,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20098,10 +20106,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20217,10 +20225,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20332,10 +20340,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20449,10 +20457,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20568,10 +20576,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20685,10 +20693,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20714,7 +20722,7 @@
         <v>175</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M150" t="s" s="2">
         <v>426</v>
@@ -20802,10 +20810,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20919,10 +20927,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21038,10 +21046,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21157,13 +21165,13 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D154" t="s" s="2">
         <v>78</v>
@@ -21188,16 +21196,16 @@
         <v>320</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>78</v>
@@ -21226,7 +21234,7 @@
       </c>
       <c r="Y154" s="2"/>
       <c r="Z154" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>78</v>
@@ -21244,7 +21252,7 @@
         <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21262,24 +21270,24 @@
         <v>78</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21391,10 +21399,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21508,10 +21516,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21627,10 +21635,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21742,10 +21750,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21859,10 +21867,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21978,10 +21986,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22095,10 +22103,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22124,7 +22132,7 @@
         <v>175</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M162" t="s" s="2">
         <v>426</v>
@@ -22212,10 +22220,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22329,10 +22337,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22448,10 +22456,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22567,13 +22575,13 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D166" t="s" s="2">
         <v>78</v>
@@ -22598,16 +22606,16 @@
         <v>320</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>78</v>
@@ -22636,7 +22644,7 @@
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>78</v>
@@ -22654,7 +22662,7 @@
         <v>78</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22669,27 +22677,27 @@
         <v>101</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22801,10 +22809,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22916,13 +22924,13 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>78</v>
@@ -22944,13 +22952,13 @@
         <v>78</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -23033,10 +23041,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23148,10 +23156,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23263,10 +23271,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23306,7 +23314,7 @@
       </c>
       <c r="Q172" s="2"/>
       <c r="R172" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="S172" t="s" s="2">
         <v>78</v>
@@ -23380,10 +23388,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23412,7 +23420,7 @@
         <v>230</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23424,7 +23432,7 @@
         <v>78</v>
       </c>
       <c r="S173" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="T173" t="s" s="2">
         <v>78</v>
@@ -23443,7 +23451,7 @@
       </c>
       <c r="Y173" s="2"/>
       <c r="Z173" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>78</v>
@@ -23493,10 +23501,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23612,10 +23620,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23731,13 +23739,13 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D176" t="s" s="2">
         <v>78</v>
@@ -23762,16 +23770,16 @@
         <v>320</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>78</v>
@@ -23800,7 +23808,7 @@
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>78</v>
@@ -23818,7 +23826,7 @@
         <v>78</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
@@ -23833,27 +23841,27 @@
         <v>101</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23965,10 +23973,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24080,13 +24088,13 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>78</v>
@@ -24108,13 +24116,13 @@
         <v>78</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -24197,10 +24205,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24312,10 +24320,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24427,10 +24435,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24470,7 +24478,7 @@
       </c>
       <c r="Q182" s="2"/>
       <c r="R182" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="S182" t="s" s="2">
         <v>78</v>
@@ -24544,10 +24552,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24576,7 +24584,7 @@
         <v>230</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -24588,7 +24596,7 @@
         <v>78</v>
       </c>
       <c r="S183" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="T183" t="s" s="2">
         <v>78</v>
@@ -24607,7 +24615,7 @@
       </c>
       <c r="Y183" s="2"/>
       <c r="Z183" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>78</v>
@@ -24657,10 +24665,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24776,10 +24784,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24895,13 +24903,13 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D186" t="s" s="2">
         <v>78</v>
@@ -24926,16 +24934,16 @@
         <v>320</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>78</v>
@@ -24964,7 +24972,7 @@
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>78</v>
@@ -24982,7 +24990,7 @@
         <v>78</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -25000,24 +25008,24 @@
         <v>78</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN186" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25129,10 +25137,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25244,13 +25252,13 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D189" t="s" s="2">
         <v>78</v>
@@ -25272,13 +25280,13 @@
         <v>78</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -25361,10 +25369,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25476,10 +25484,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25591,10 +25599,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25634,7 +25642,7 @@
       </c>
       <c r="Q192" s="2"/>
       <c r="R192" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="S192" t="s" s="2">
         <v>78</v>
@@ -25708,10 +25716,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25740,7 +25748,7 @@
         <v>230</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
@@ -25752,7 +25760,7 @@
         <v>78</v>
       </c>
       <c r="S193" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="T193" t="s" s="2">
         <v>78</v>
@@ -25771,7 +25779,7 @@
       </c>
       <c r="Y193" s="2"/>
       <c r="Z193" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>78</v>
@@ -25821,10 +25829,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25940,10 +25948,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26059,13 +26067,13 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D196" t="s" s="2">
         <v>78</v>
@@ -26090,16 +26098,16 @@
         <v>320</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>78</v>
@@ -26127,10 +26135,10 @@
         <v>165</v>
       </c>
       <c r="Y196" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z196" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA196" t="s" s="2">
         <v>78</v>
@@ -26148,7 +26156,7 @@
         <v>78</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>79</v>
@@ -26166,24 +26174,24 @@
         <v>78</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN196" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26295,10 +26303,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26410,13 +26418,13 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D199" t="s" s="2">
         <v>78</v>
@@ -26438,13 +26446,13 @@
         <v>78</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -26527,10 +26535,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26642,10 +26650,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26757,10 +26765,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26800,7 +26808,7 @@
       </c>
       <c r="Q202" s="2"/>
       <c r="R202" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="S202" t="s" s="2">
         <v>78</v>
@@ -26874,10 +26882,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -26906,7 +26914,7 @@
         <v>230</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
@@ -26918,7 +26926,7 @@
         <v>78</v>
       </c>
       <c r="S203" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="T203" t="s" s="2">
         <v>78</v>
@@ -26937,7 +26945,7 @@
       </c>
       <c r="Y203" s="2"/>
       <c r="Z203" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>78</v>
@@ -26987,10 +26995,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27106,10 +27114,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27225,10 +27233,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27254,16 +27262,16 @@
         <v>103</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="O206" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="P206" t="s" s="2">
         <v>78</v>
@@ -27312,7 +27320,7 @@
         <v>78</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>79</v>
@@ -27327,16 +27335,16 @@
         <v>101</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AL206" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AM206" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>78</v>
@@ -27344,10 +27352,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27373,16 +27381,16 @@
         <v>103</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="O207" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>78</v>
@@ -27431,7 +27439,7 @@
         <v>78</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>79</v>
@@ -27446,13 +27454,13 @@
         <v>101</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AL207" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM207" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AN207" t="s" s="2">
         <v>78</v>
@@ -27463,10 +27471,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27489,19 +27497,19 @@
         <v>78</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="O208" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="P208" t="s" s="2">
         <v>78</v>
@@ -27538,7 +27546,7 @@
         <v>78</v>
       </c>
       <c r="AB208" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AC208" s="2"/>
       <c r="AD208" t="s" s="2">
@@ -27548,7 +27556,7 @@
         <v>116</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>79</v>
@@ -27560,19 +27568,19 @@
         <v>207</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AK208" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AL208" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AM208" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AO208" t="s" s="2">
         <v>78</v>
@@ -27580,10 +27588,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27695,10 +27703,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27812,13 +27820,13 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="B211" t="s" s="2">
         <v>701</v>
       </c>
-      <c r="B211" t="s" s="2">
-        <v>700</v>
-      </c>
       <c r="C211" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D211" t="s" s="2">
         <v>78</v>
@@ -27840,13 +27848,13 @@
         <v>78</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
@@ -27929,10 +27937,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -27958,10 +27966,10 @@
         <v>175</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -27991,10 +27999,10 @@
         <v>314</v>
       </c>
       <c r="Y212" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="Z212" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>78</v>
@@ -28012,7 +28020,7 @@
         <v>78</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
@@ -28021,7 +28029,7 @@
         <v>89</v>
       </c>
       <c r="AI212" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AJ212" t="s" s="2">
         <v>101</v>
@@ -28030,13 +28038,13 @@
         <v>78</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AM212" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AN212" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AO212" t="s" s="2">
         <v>78</v>
@@ -28044,10 +28052,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28073,16 +28081,16 @@
         <v>103</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O213" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>78</v>
@@ -28131,7 +28139,7 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>79</v>
@@ -28149,10 +28157,10 @@
         <v>78</v>
       </c>
       <c r="AL213" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AN213" t="s" s="2">
         <v>347</v>
@@ -28163,10 +28171,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28192,16 +28200,16 @@
         <v>175</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="O214" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -28229,10 +28237,10 @@
         <v>314</v>
       </c>
       <c r="Y214" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="Z214" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>78</v>
@@ -28250,7 +28258,7 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
@@ -28268,13 +28276,13 @@
         <v>78</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>78</v>
@@ -28282,10 +28290,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28308,16 +28316,16 @@
         <v>90</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="N215" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
@@ -28367,7 +28375,7 @@
         <v>78</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
@@ -28399,10 +28407,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28428,10 +28436,10 @@
         <v>229</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -28482,7 +28490,7 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -28503,7 +28511,7 @@
         <v>198</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AN216" t="s" s="2">
         <v>354</v>
@@ -28514,13 +28522,13 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D217" t="s" s="2">
         <v>78</v>
@@ -28542,19 +28550,19 @@
         <v>78</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="O217" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>78</v>
@@ -28603,7 +28611,7 @@
         <v>78</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>79</v>
@@ -28615,19 +28623,19 @@
         <v>207</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AK217" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL217" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AM217" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>78</v>
@@ -28635,10 +28643,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28750,10 +28758,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -28867,13 +28875,13 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D220" t="s" s="2">
         <v>78</v>
@@ -28895,13 +28903,13 @@
         <v>78</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
@@ -28984,10 +28992,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29099,10 +29107,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29214,10 +29222,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29257,7 +29265,7 @@
       </c>
       <c r="Q223" s="2"/>
       <c r="R223" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="S223" t="s" s="2">
         <v>78</v>
@@ -29331,10 +29339,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29363,7 +29371,7 @@
         <v>230</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -29375,7 +29383,7 @@
         <v>78</v>
       </c>
       <c r="S224" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="T224" t="s" s="2">
         <v>78</v>
@@ -29394,7 +29402,7 @@
       </c>
       <c r="Y224" s="2"/>
       <c r="Z224" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AA224" t="s" s="2">
         <v>78</v>
@@ -29444,13 +29452,13 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D225" t="s" s="2">
         <v>78</v>
@@ -29472,13 +29480,13 @@
         <v>78</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -29561,10 +29569,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -29676,10 +29684,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -29793,13 +29801,13 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D228" t="s" s="2">
         <v>78</v>
@@ -29824,7 +29832,7 @@
         <v>110</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="M228" t="s" s="2">
         <v>201</v>
@@ -29910,10 +29918,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30025,10 +30033,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30140,10 +30148,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30183,7 +30191,7 @@
       </c>
       <c r="Q231" s="2"/>
       <c r="R231" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="S231" t="s" s="2">
         <v>78</v>
@@ -30257,10 +30265,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30289,7 +30297,7 @@
         <v>230</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
@@ -30320,7 +30328,7 @@
       </c>
       <c r="Y232" s="2"/>
       <c r="Z232" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>78</v>
@@ -30370,10 +30378,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C233" t="s" s="2">
         <v>209</v>
@@ -30401,7 +30409,7 @@
         <v>110</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="M233" t="s" s="2">
         <v>201</v>
@@ -30487,10 +30495,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30602,10 +30610,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30717,10 +30725,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -30834,10 +30842,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -30866,7 +30874,7 @@
         <v>230</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N237" s="2"/>
       <c r="O237" s="2"/>
@@ -30949,13 +30957,13 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D238" t="s" s="2">
         <v>78</v>
@@ -31066,10 +31074,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -31181,10 +31189,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31296,10 +31304,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31339,7 +31347,7 @@
       </c>
       <c r="Q241" s="2"/>
       <c r="R241" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="S241" t="s" s="2">
         <v>78</v>
@@ -31413,10 +31421,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -31445,7 +31453,7 @@
         <v>230</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
@@ -31528,13 +31536,13 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D243" t="s" s="2">
         <v>78</v>
@@ -31559,7 +31567,7 @@
         <v>110</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="M243" t="s" s="2">
         <v>201</v>
@@ -31645,10 +31653,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31760,10 +31768,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -31875,10 +31883,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -31918,7 +31926,7 @@
       </c>
       <c r="Q246" s="2"/>
       <c r="R246" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="S246" t="s" s="2">
         <v>78</v>
@@ -31992,10 +32000,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32024,7 +32032,7 @@
         <v>230</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N247" s="2"/>
       <c r="O247" s="2"/>
@@ -32107,13 +32115,13 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D248" t="s" s="2">
         <v>78</v>
@@ -32224,10 +32232,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -32339,10 +32347,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -32454,10 +32462,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32497,7 +32505,7 @@
       </c>
       <c r="Q251" s="2"/>
       <c r="R251" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="S251" t="s" s="2">
         <v>78</v>
@@ -32571,10 +32579,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32603,7 +32611,7 @@
         <v>230</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N252" s="2"/>
       <c r="O252" s="2"/>
@@ -32686,13 +32694,13 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D253" t="s" s="2">
         <v>78</v>
@@ -32717,7 +32725,7 @@
         <v>110</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="M253" t="s" s="2">
         <v>201</v>
@@ -32803,10 +32811,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -32918,10 +32926,10 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -33033,10 +33041,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -33076,7 +33084,7 @@
       </c>
       <c r="Q256" s="2"/>
       <c r="R256" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="S256" t="s" s="2">
         <v>78</v>
@@ -33150,10 +33158,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -33182,7 +33190,7 @@
         <v>230</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N257" s="2"/>
       <c r="O257" s="2"/>
@@ -33265,13 +33273,13 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D258" t="s" s="2">
         <v>78</v>
@@ -33296,7 +33304,7 @@
         <v>110</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M258" t="s" s="2">
         <v>201</v>
@@ -33382,10 +33390,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33497,10 +33505,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33612,10 +33620,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33655,7 +33663,7 @@
       </c>
       <c r="Q261" s="2"/>
       <c r="R261" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="S261" t="s" s="2">
         <v>78</v>
@@ -33729,10 +33737,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33761,7 +33769,7 @@
         <v>230</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N262" s="2"/>
       <c r="O262" s="2"/>
@@ -33844,10 +33852,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -33887,7 +33895,7 @@
       </c>
       <c r="Q263" s="2"/>
       <c r="R263" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="S263" t="s" s="2">
         <v>78</v>
@@ -33961,10 +33969,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -33987,13 +33995,13 @@
         <v>78</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="L264" t="s" s="2">
         <v>230</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N264" s="2"/>
       <c r="O264" s="2"/>
@@ -34076,10 +34084,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -34105,10 +34113,10 @@
         <v>175</v>
       </c>
       <c r="L265" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M265" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N265" s="2"/>
       <c r="O265" s="2"/>
@@ -34120,7 +34128,7 @@
         <v>78</v>
       </c>
       <c r="S265" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="T265" t="s" s="2">
         <v>78</v>
@@ -34138,10 +34146,10 @@
         <v>314</v>
       </c>
       <c r="Y265" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="Z265" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AA265" t="s" s="2">
         <v>78</v>
@@ -34159,7 +34167,7 @@
         <v>78</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>79</v>
@@ -34168,7 +34176,7 @@
         <v>89</v>
       </c>
       <c r="AI265" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AJ265" t="s" s="2">
         <v>101</v>
@@ -34177,13 +34185,13 @@
         <v>78</v>
       </c>
       <c r="AL265" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AM265" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AN265" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AO265" t="s" s="2">
         <v>78</v>
@@ -34191,10 +34199,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -34220,16 +34228,16 @@
         <v>103</v>
       </c>
       <c r="L266" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N266" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O266" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="P266" t="s" s="2">
         <v>78</v>
@@ -34278,7 +34286,7 @@
         <v>78</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>79</v>
@@ -34296,10 +34304,10 @@
         <v>78</v>
       </c>
       <c r="AL266" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AM266" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AN266" t="s" s="2">
         <v>347</v>
@@ -34310,10 +34318,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -34339,16 +34347,16 @@
         <v>175</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N267" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="O267" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P267" t="s" s="2">
         <v>78</v>
@@ -34376,10 +34384,10 @@
         <v>314</v>
       </c>
       <c r="Y267" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="Z267" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AA267" t="s" s="2">
         <v>78</v>
@@ -34397,7 +34405,7 @@
         <v>78</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>79</v>
@@ -34415,13 +34423,13 @@
         <v>78</v>
       </c>
       <c r="AL267" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AM267" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AN267" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AO267" t="s" s="2">
         <v>78</v>
@@ -34429,10 +34437,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -34455,16 +34463,16 @@
         <v>90</v>
       </c>
       <c r="K268" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="N268" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="O268" s="2"/>
       <c r="P268" t="s" s="2">
@@ -34514,7 +34522,7 @@
         <v>78</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>79</v>
@@ -34546,10 +34554,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -34575,10 +34583,10 @@
         <v>229</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N269" s="2"/>
       <c r="O269" s="2"/>
@@ -34629,7 +34637,7 @@
         <v>78</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>79</v>
@@ -34650,7 +34658,7 @@
         <v>198</v>
       </c>
       <c r="AM269" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AN269" t="s" s="2">
         <v>354</v>
@@ -34661,10 +34669,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -34687,19 +34695,19 @@
         <v>78</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="N270" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="O270" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="P270" t="s" s="2">
         <v>78</v>
@@ -34748,7 +34756,7 @@
         <v>78</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>79</v>
@@ -34760,19 +34768,19 @@
         <v>207</v>
       </c>
       <c r="AJ270" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AK270" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AL270" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AM270" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AN270" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AO270" t="s" s="2">
         <v>78</v>
@@ -34780,10 +34788,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -34806,17 +34814,17 @@
         <v>90</v>
       </c>
       <c r="K271" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="L271" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="M271" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="N271" s="2"/>
       <c r="O271" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="P271" t="s" s="2">
         <v>78</v>
@@ -34865,7 +34873,7 @@
         <v>78</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>79</v>
@@ -34883,10 +34891,10 @@
         <v>78</v>
       </c>
       <c r="AL271" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM271" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AN271" t="s" s="2">
         <v>107</v>
@@ -34897,10 +34905,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -35012,10 +35020,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -35129,10 +35137,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -35158,13 +35166,13 @@
         <v>103</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="M274" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="N274" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="O274" s="2"/>
       <c r="P274" t="s" s="2">
@@ -35214,7 +35222,7 @@
         <v>78</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AG274" t="s" s="2">
         <v>79</v>
@@ -35223,7 +35231,7 @@
         <v>89</v>
       </c>
       <c r="AI274" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="AJ274" t="s" s="2">
         <v>101</v>
@@ -35246,10 +35254,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -35275,13 +35283,13 @@
         <v>136</v>
       </c>
       <c r="L275" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="M275" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="N275" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="O275" s="2"/>
       <c r="P275" t="s" s="2">
@@ -35311,7 +35319,7 @@
       </c>
       <c r="Y275" s="2"/>
       <c r="Z275" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AA275" t="s" s="2">
         <v>78</v>
@@ -35329,7 +35337,7 @@
         <v>78</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>79</v>
@@ -35361,10 +35369,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -35390,13 +35398,13 @@
         <v>296</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="N276" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="O276" s="2"/>
       <c r="P276" t="s" s="2">
@@ -35446,7 +35454,7 @@
         <v>78</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>79</v>
@@ -35467,7 +35475,7 @@
         <v>78</v>
       </c>
       <c r="AM276" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="AN276" t="s" s="2">
         <v>78</v>
@@ -35478,10 +35486,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -35507,13 +35515,13 @@
         <v>103</v>
       </c>
       <c r="L277" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="M277" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="N277" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="O277" s="2"/>
       <c r="P277" t="s" s="2">
@@ -35563,7 +35571,7 @@
         <v>78</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>79</v>
@@ -35595,10 +35603,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35621,19 +35629,19 @@
         <v>78</v>
       </c>
       <c r="K278" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="L278" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="M278" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="N278" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="O278" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="P278" t="s" s="2">
         <v>78</v>
@@ -35682,7 +35690,7 @@
         <v>78</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>79</v>
@@ -35703,7 +35711,7 @@
         <v>78</v>
       </c>
       <c r="AM278" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="AN278" t="s" s="2">
         <v>78</v>
@@ -35714,10 +35722,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -35829,10 +35837,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -35946,14 +35954,14 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E281" s="2"/>
       <c r="F281" t="s" s="2">
@@ -35975,10 +35983,10 @@
         <v>110</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N281" t="s" s="2">
         <v>113</v>
@@ -36033,7 +36041,7 @@
         <v>78</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>79</v>
@@ -36065,10 +36073,10 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -36094,14 +36102,14 @@
         <v>320</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="N282" s="2"/>
       <c r="O282" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="P282" t="s" s="2">
         <v>78</v>
@@ -36129,10 +36137,10 @@
         <v>157</v>
       </c>
       <c r="Y282" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="Z282" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="AA282" t="s" s="2">
         <v>78</v>
@@ -36150,7 +36158,7 @@
         <v>78</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>79</v>
@@ -36171,7 +36179,7 @@
         <v>78</v>
       </c>
       <c r="AM282" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="AN282" t="s" s="2">
         <v>78</v>
@@ -36182,10 +36190,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -36208,17 +36216,17 @@
         <v>78</v>
       </c>
       <c r="K283" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="L283" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="M283" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="N283" s="2"/>
       <c r="O283" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="P283" t="s" s="2">
         <v>78</v>
@@ -36267,7 +36275,7 @@
         <v>78</v>
       </c>
       <c r="AF283" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="AG283" t="s" s="2">
         <v>79</v>
@@ -36285,10 +36293,10 @@
         <v>78</v>
       </c>
       <c r="AL283" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="AM283" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="AN283" t="s" s="2">
         <v>78</v>
@@ -36299,10 +36307,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -36325,17 +36333,17 @@
         <v>78</v>
       </c>
       <c r="K284" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="L284" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="M284" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N284" s="2"/>
       <c r="O284" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="P284" t="s" s="2">
         <v>78</v>
@@ -36384,7 +36392,7 @@
         <v>78</v>
       </c>
       <c r="AF284" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="AG284" t="s" s="2">
         <v>79</v>
@@ -36396,19 +36404,19 @@
         <v>207</v>
       </c>
       <c r="AJ284" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="AK284" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL284" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AM284" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AN284" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AO284" t="s" s="2">
         <v>78</v>
@@ -36416,10 +36424,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -36442,19 +36450,19 @@
         <v>78</v>
       </c>
       <c r="K285" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="L285" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="M285" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="N285" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="O285" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="P285" t="s" s="2">
         <v>78</v>
@@ -36503,7 +36511,7 @@
         <v>78</v>
       </c>
       <c r="AF285" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="AG285" t="s" s="2">
         <v>79</v>
@@ -36521,13 +36529,13 @@
         <v>78</v>
       </c>
       <c r="AL285" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AM285" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AN285" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AO285" t="s" s="2">
         <v>78</v>
@@ -36535,10 +36543,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -36561,17 +36569,17 @@
         <v>78</v>
       </c>
       <c r="K286" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="N286" s="2"/>
       <c r="O286" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="P286" t="s" s="2">
         <v>78</v>
@@ -36620,7 +36628,7 @@
         <v>78</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>79</v>

--- a/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T11:50:43+00:00</t>
+    <t>2024-04-26T07:42:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
